--- a/output/ai-shinryou-db/text/2026/hosei-tsuuchi-i/2026_別添３（歯科診療所用）［46KB］_20260501.xlsx
+++ b/output/ai-shinryou-db/text/2026/hosei-tsuuchi-i/2026_別添３（歯科診療所用）［46KB］_20260501.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="249" documentId="13_ncr:1_{0DCDE20B-E308-474E-B601-1C14402EDCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF76CF73-F735-4752-9470-6B948B920FEC}"/>
+  <xr:revisionPtr revIDLastSave="283" documentId="13_ncr:1_{0DCDE20B-E308-474E-B601-1C14402EDCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0446CA9B-C1F0-4480-BEAC-43F6E00EEA6F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{15D408F1-8FA9-4BF6-A58A-0BFAEE5720F3}"/>
   </bookViews>
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">【歯科診療所用】チェックリスト!$B$10:$I$13</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">【歯科診療所用】チェックリスト!$B$1:$I$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">【歯科診療所用】チェックリスト!$B$1:$I$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">【歯科診療所用】チェックリスト!$1:$10</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="44">
   <si>
     <t>チェックリストの利用方法　　　　　　</t>
     <rPh sb="8" eb="10">
@@ -583,6 +583,9 @@
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
+  <si>
+    <t>地域支援・外来医薬品供給対応体制加算</t>
+  </si>
 </sst>
 </file>
 
@@ -591,7 +594,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@" x16r2:formatCode16="[$-ja-JP-x-gannen]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -786,6 +789,21 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1016,7 +1034,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1144,6 +1162,12 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1981,24 +2005,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
@@ -2062,7 +2086,7 @@
     <tabColor rgb="FF00B050"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
@@ -2079,23 +2103,23 @@
   <sheetData>
     <row r="1" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="32"/>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
     </row>
     <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="H3" s="12" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="13">
-        <v>46132</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -2104,16 +2128,16 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
     </row>
     <row r="6" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="15" t="s">
@@ -2121,16 +2145,16 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
     </row>
     <row r="8" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C8" s="15"/>
@@ -2290,7 +2314,7 @@
       </c>
       <c r="I15" s="38"/>
     </row>
-    <row r="16" spans="1:9" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9" s="44" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="B16" s="23">
         <v>6</v>
       </c>
@@ -2300,19 +2324,19 @@
       <c r="D16" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="E16" s="42" t="s">
         <v>24</v>
       </c>
       <c r="F16" s="27" t="s">
         <v>25</v>
       </c>
       <c r="G16" s="40" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="H16" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="I16" s="41"/>
+      <c r="I16" s="45"/>
     </row>
     <row r="17" spans="2:9" ht="13.5" x14ac:dyDescent="0.4">
       <c r="B17" s="23">
@@ -2330,13 +2354,13 @@
       <c r="F17" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="G17" s="39" t="s">
-        <v>31</v>
+      <c r="G17" s="40" t="s">
+        <v>30</v>
       </c>
       <c r="H17" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="I17" s="38"/>
+      <c r="I17" s="41"/>
     </row>
     <row r="18" spans="2:9" ht="13.5" x14ac:dyDescent="0.4">
       <c r="B18" s="23">
@@ -2355,7 +2379,7 @@
         <v>25</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H18" s="37" t="s">
         <v>25</v>
@@ -2379,7 +2403,7 @@
         <v>25</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H19" s="37" t="s">
         <v>25</v>
@@ -2403,7 +2427,7 @@
         <v>25</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H20" s="37" t="s">
         <v>25</v>
@@ -2420,14 +2444,14 @@
       <c r="D21" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="29" t="s">
-        <v>35</v>
+      <c r="E21" s="26" t="s">
+        <v>24</v>
       </c>
       <c r="F21" s="27" t="s">
         <v>25</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H21" s="37" t="s">
         <v>25</v>
@@ -2451,12 +2475,36 @@
         <v>25</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H22" s="37" t="s">
         <v>25</v>
       </c>
       <c r="I22" s="38"/>
+    </row>
+    <row r="23" spans="2:9" ht="13.5" x14ac:dyDescent="0.4">
+      <c r="B23" s="23">
+        <v>13</v>
+      </c>
+      <c r="C23" s="24">
+        <v>46174</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="I23" s="38"/>
     </row>
   </sheetData>
   <autoFilter ref="B10:I13" xr:uid="{AD3731C8-59BC-4CA6-AFC8-34DE49416B4C}"/>
@@ -2466,7 +2514,7 @@
     <mergeCell ref="B1:I1"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
-  <conditionalFormatting sqref="F11:F22 H11:H22">
+  <conditionalFormatting sqref="F11:F23 H11:H23">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"☑"</formula>
     </cfRule>
@@ -2481,7 +2529,7 @@
           <x14:formula1>
             <xm:f>リスト!$A$1:$A$2</xm:f>
           </x14:formula1>
-          <xm:sqref>F11:F22 H11:H22</xm:sqref>
+          <xm:sqref>F11:F23 H11:H23</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2515,12 +2563,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="263dbbe5-076b-4606-a03b-9598f5f2f35a" xsi:nil="true"/>
+    <Owner xmlns="33f003c0-0d95-44a8-96ef-b6b435aaba2f">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="33f003c0-0d95-44a8-96ef-b6b435aaba2f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2757,27 +2814,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="263dbbe5-076b-4606-a03b-9598f5f2f35a" xsi:nil="true"/>
-    <Owner xmlns="33f003c0-0d95-44a8-96ef-b6b435aaba2f">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="33f003c0-0d95-44a8-96ef-b6b435aaba2f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C264523C-0E05-4792-95D0-1D3132DF9B57}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD6B6078-AA6D-4299-8233-B3608D4D1319}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="33f003c0-0d95-44a8-96ef-b6b435aaba2f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2802,18 +2859,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD6B6078-AA6D-4299-8233-B3608D4D1319}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C264523C-0E05-4792-95D0-1D3132DF9B57}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="33f003c0-0d95-44a8-96ef-b6b435aaba2f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>